--- a/data/Center Master.xlsx
+++ b/data/Center Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Praveen SN\PycharmProjects\website\mis_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781902B8-96A9-40FC-858F-82BFE6813E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE3E0B3-3429-44B1-960E-65FA89F2F491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{65DEC15B-CB0E-4668-98DE-92AB018A28B1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7074,59 +7074,59 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6 B2:B126">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C26">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38:C44">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C53">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68">
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C112">
-    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:C118">
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C119 C126">
-    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45 K47 K49 K59">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B126 C2:C6">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G73 K2:K73" xr:uid="{0A916525-D2E7-410A-851E-5D90B6CAD0BD}">

--- a/data/Center Master.xlsx
+++ b/data/Center Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Praveen SN\PycharmProjects\website\mis_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE3E0B3-3429-44B1-960E-65FA89F2F491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E31FF8-C96B-4784-BE89-E76C37954C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{65DEC15B-CB0E-4668-98DE-92AB018A28B1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="629">
   <si>
     <t>Entity</t>
   </si>
@@ -1960,6 +1960,9 @@
   </si>
   <si>
     <t>NSK-01</t>
+  </si>
+  <si>
+    <t>Pin code</t>
   </si>
 </sst>
 </file>
@@ -2649,7 +2652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{209D6F5C-C123-4A7D-95B6-A17DEAA21998}">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.73046875" bestFit="1" customWidth="1"/>
@@ -2659,11 +2662,12 @@
     <col min="5" max="5" width="7.9296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="17.06640625" customWidth="1"/>
-    <col min="11" max="11" width="28.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.06640625" customWidth="1"/>
+    <col min="9" max="11" width="17.06640625" customWidth="1"/>
+    <col min="12" max="12" width="28.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2685,20 +2689,23 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I1" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -2720,20 +2727,23 @@
       <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4">
+        <v>563122</v>
+      </c>
+      <c r="I2" t="s">
         <v>499</v>
-      </c>
-      <c r="I2" t="s">
-        <v>464</v>
       </c>
       <c r="J2" t="s">
         <v>464</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" t="s">
+        <v>464</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -2755,20 +2765,23 @@
       <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4">
+        <v>560048</v>
+      </c>
+      <c r="I3" t="s">
         <v>500</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>501</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>502</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -2790,20 +2803,23 @@
       <c r="G4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4">
+        <v>679573</v>
+      </c>
+      <c r="I4" t="s">
         <v>503</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2825,20 +2841,23 @@
       <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4">
+        <v>700014</v>
+      </c>
+      <c r="I5" t="s">
         <v>504</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>156</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>505</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -2860,20 +2879,23 @@
       <c r="G6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="4">
+        <v>302012</v>
+      </c>
+      <c r="I6" t="s">
         <v>506</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>507</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>508</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -2895,20 +2917,23 @@
       <c r="G7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="4">
+        <v>560062</v>
+      </c>
+      <c r="I7" t="s">
         <v>509</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>501</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>510</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="L7" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -2930,20 +2955,23 @@
       <c r="G8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="4">
+        <v>583104</v>
+      </c>
+      <c r="I8" t="s">
         <v>511</v>
-      </c>
-      <c r="I8" t="s">
-        <v>29</v>
       </c>
       <c r="J8" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -2965,20 +2993,23 @@
       <c r="G9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="4">
+        <v>586103</v>
+      </c>
+      <c r="I9" t="s">
         <v>512</v>
-      </c>
-      <c r="I9" t="s">
-        <v>33</v>
       </c>
       <c r="J9" t="s">
         <v>33</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -3000,20 +3031,23 @@
       <c r="G10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="4">
+        <v>575004</v>
+      </c>
+      <c r="I10" t="s">
         <v>513</v>
-      </c>
-      <c r="I10" t="s">
-        <v>514</v>
       </c>
       <c r="J10" t="s">
         <v>514</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" t="s">
+        <v>514</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -3035,20 +3069,23 @@
       <c r="G11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="4">
+        <v>577005</v>
+      </c>
+      <c r="I11" t="s">
         <v>515</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
       </c>
       <c r="J11" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>7</v>
       </c>
@@ -3070,20 +3107,23 @@
       <c r="G12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="4">
+        <v>585101</v>
+      </c>
+      <c r="I12" t="s">
         <v>516</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>46</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>517</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
@@ -3105,20 +3145,23 @@
       <c r="G13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="4">
+        <v>635109</v>
+      </c>
+      <c r="I13" t="s">
         <v>518</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>50</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>519</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="15" t="s">
         <v>7</v>
       </c>
@@ -3140,20 +3183,23 @@
       <c r="G14" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="4">
+        <v>590008</v>
+      </c>
+      <c r="I14" t="s">
         <v>520</v>
-      </c>
-      <c r="I14" t="s">
-        <v>493</v>
       </c>
       <c r="J14" t="s">
         <v>493</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" t="s">
+        <v>493</v>
+      </c>
+      <c r="L14" s="15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
@@ -3175,20 +3221,23 @@
       <c r="G15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="4">
+        <v>560049</v>
+      </c>
+      <c r="I15" t="s">
         <v>521</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>501</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>522</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="L15" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
@@ -3210,20 +3259,23 @@
       <c r="G16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="4">
+        <v>560004</v>
+      </c>
+      <c r="I16" t="s">
         <v>509</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>501</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>510</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="L16" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>7</v>
       </c>
@@ -3245,20 +3297,23 @@
       <c r="G17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="4">
+        <v>560032</v>
+      </c>
+      <c r="I17" t="s">
         <v>521</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>501</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>522</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="L17" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>7</v>
       </c>
@@ -3280,20 +3335,23 @@
       <c r="G18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="4">
+        <v>560022</v>
+      </c>
+      <c r="I18" t="s">
         <v>523</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>501</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>524</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="L18" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
@@ -3315,20 +3373,23 @@
       <c r="G19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="4">
+        <v>140401</v>
+      </c>
+      <c r="I19" t="s">
         <v>525</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>526</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>527</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="L19" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>56</v>
       </c>
@@ -3350,20 +3411,23 @@
       <c r="G20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="4">
+        <v>605110</v>
+      </c>
+      <c r="I20" t="s">
         <v>528</v>
-      </c>
-      <c r="I20" t="s">
-        <v>63</v>
       </c>
       <c r="J20" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>56</v>
       </c>
@@ -3385,20 +3449,23 @@
       <c r="G21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="4">
+        <v>635109</v>
+      </c>
+      <c r="I21" t="s">
         <v>518</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>50</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>519</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="L21" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>56</v>
       </c>
@@ -3420,20 +3487,23 @@
       <c r="G22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="4">
+        <v>786150</v>
+      </c>
+      <c r="I22" t="s">
         <v>529</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>530</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>531</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="L22" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
@@ -3455,20 +3525,23 @@
       <c r="G23" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="4">
+        <v>396230</v>
+      </c>
+      <c r="I23" t="s">
         <v>532</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>533</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>534</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="L23" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>56</v>
       </c>
@@ -3490,20 +3563,23 @@
       <c r="G24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="4">
+        <v>370201</v>
+      </c>
+      <c r="I24" t="s">
         <v>535</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>82</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>536</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>56</v>
       </c>
@@ -3525,20 +3601,23 @@
       <c r="G25" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="4">
+        <v>415722</v>
+      </c>
+      <c r="I25" t="s">
         <v>537</v>
-      </c>
-      <c r="I25" t="s">
-        <v>87</v>
       </c>
       <c r="J25" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" t="s">
+        <v>87</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>56</v>
       </c>
@@ -3560,20 +3639,23 @@
       <c r="G26" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="4">
+        <v>210502</v>
+      </c>
+      <c r="I26" t="s">
         <v>538</v>
-      </c>
-      <c r="I26" t="s">
-        <v>92</v>
       </c>
       <c r="J26" t="s">
         <v>92</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
@@ -3595,20 +3677,23 @@
       <c r="G27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="4">
+        <v>207001</v>
+      </c>
+      <c r="I27" t="s">
         <v>539</v>
-      </c>
-      <c r="I27" t="s">
-        <v>97</v>
       </c>
       <c r="J27" t="s">
         <v>97</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" t="s">
+        <v>97</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>56</v>
       </c>
@@ -3630,20 +3715,23 @@
       <c r="G28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="4">
+        <v>249403</v>
+      </c>
+      <c r="I28" t="s">
         <v>540</v>
-      </c>
-      <c r="I28" t="s">
-        <v>101</v>
       </c>
       <c r="J28" t="s">
         <v>101</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" t="s">
+        <v>101</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -3665,20 +3753,23 @@
       <c r="G29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="4">
+        <v>570004</v>
+      </c>
+      <c r="I29" t="s">
         <v>541</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>542</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>543</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="L29" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" s="16" t="s">
         <v>7</v>
       </c>
@@ -3700,20 +3791,23 @@
       <c r="G30" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="4">
+        <v>560050</v>
+      </c>
+      <c r="I30" t="s">
         <v>509</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>501</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>510</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="L30" s="16" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" s="16" t="s">
         <v>7</v>
       </c>
@@ -3735,20 +3829,23 @@
       <c r="G31" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="4">
+        <v>400024</v>
+      </c>
+      <c r="I31" t="s">
         <v>544</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>436</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>545</v>
       </c>
-      <c r="K31" s="16" t="s">
+      <c r="L31" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" s="16" t="s">
         <v>7</v>
       </c>
@@ -3770,20 +3867,23 @@
       <c r="G32" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="4">
+        <v>500004</v>
+      </c>
+      <c r="I32" t="s">
         <v>546</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>530</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>547</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="L32" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
         <v>7</v>
       </c>
@@ -3805,20 +3905,23 @@
       <c r="G33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="4">
+        <v>562114</v>
+      </c>
+      <c r="I33" t="s">
         <v>500</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>501</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>502</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="L33" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
         <v>7</v>
       </c>
@@ -3840,20 +3943,23 @@
       <c r="G34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="4">
+        <v>751010</v>
+      </c>
+      <c r="I34" t="s">
         <v>548</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>474</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>549</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="L34" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
         <v>7</v>
       </c>
@@ -3875,20 +3981,23 @@
       <c r="G35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="4">
+        <v>831015</v>
+      </c>
+      <c r="I35" t="s">
         <v>550</v>
-      </c>
-      <c r="I35" t="s">
-        <v>551</v>
       </c>
       <c r="J35" t="s">
         <v>551</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" t="s">
+        <v>551</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
         <v>7</v>
       </c>
@@ -3910,20 +4019,23 @@
       <c r="G36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="4">
+        <v>635126</v>
+      </c>
+      <c r="I36" t="s">
         <v>552</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>50</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>553</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="L36" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
         <v>7</v>
       </c>
@@ -3945,20 +4057,23 @@
       <c r="G37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="4">
+        <v>110044</v>
+      </c>
+      <c r="I37" t="s">
         <v>554</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>555</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>556</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="L37" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
         <v>7</v>
       </c>
@@ -3980,20 +4095,23 @@
       <c r="G38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="4">
+        <v>500003</v>
+      </c>
+      <c r="I38" t="s">
         <v>546</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>530</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>547</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="L38" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
         <v>7</v>
       </c>
@@ -4015,20 +4133,23 @@
       <c r="G39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="4">
+        <v>400086</v>
+      </c>
+      <c r="I39" t="s">
         <v>544</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>436</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>545</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="L39" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
         <v>7</v>
       </c>
@@ -4050,20 +4171,23 @@
       <c r="G40" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="4">
+        <v>560043</v>
+      </c>
+      <c r="I40" t="s">
         <v>521</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>501</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>522</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="L40" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="4" t="s">
         <v>7</v>
       </c>
@@ -4085,20 +4209,23 @@
       <c r="G41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="4">
+        <v>412207</v>
+      </c>
+      <c r="I41" t="s">
         <v>557</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>332</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>558</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="L41" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
         <v>7</v>
       </c>
@@ -4120,20 +4247,23 @@
       <c r="G42" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="4">
+        <v>560050</v>
+      </c>
+      <c r="I42" t="s">
         <v>509</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>501</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>510</v>
       </c>
-      <c r="K42" s="4" t="s">
+      <c r="L42" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" s="4" t="s">
         <v>7</v>
       </c>
@@ -4155,20 +4285,23 @@
       <c r="G43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="4">
+        <v>560022</v>
+      </c>
+      <c r="I43" t="s">
         <v>523</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>501</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>524</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="L43" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
         <v>7</v>
       </c>
@@ -4190,20 +4323,23 @@
       <c r="G44" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="4">
+        <v>500062</v>
+      </c>
+      <c r="I44" t="s">
         <v>546</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>530</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>547</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="L44" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A45" s="4" t="s">
         <v>7</v>
       </c>
@@ -4225,20 +4361,23 @@
       <c r="G45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="4">
+        <v>743337</v>
+      </c>
+      <c r="I45" t="s">
         <v>559</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
         <v>156</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>560</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="L45" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
         <v>7</v>
       </c>
@@ -4260,20 +4399,23 @@
       <c r="G46" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="4">
+        <v>201003</v>
+      </c>
+      <c r="I46" t="s">
         <v>561</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>555</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>562</v>
       </c>
-      <c r="K46" s="4" t="s">
+      <c r="L46" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
         <v>7</v>
       </c>
@@ -4295,20 +4437,23 @@
       <c r="G47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="4">
+        <v>700084</v>
+      </c>
+      <c r="I47" t="s">
         <v>504</v>
       </c>
-      <c r="I47" t="s">
+      <c r="J47" t="s">
         <v>156</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>505</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="L47" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
         <v>7</v>
       </c>
@@ -4330,20 +4475,23 @@
       <c r="G48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="4">
+        <v>560085</v>
+      </c>
+      <c r="I48" t="s">
         <v>509</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>501</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>510</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="L48" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
         <v>7</v>
       </c>
@@ -4365,20 +4513,23 @@
       <c r="G49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="4">
+        <v>781029</v>
+      </c>
+      <c r="I49" t="s">
         <v>563</v>
-      </c>
-      <c r="I49" t="s">
-        <v>163</v>
       </c>
       <c r="J49" t="s">
         <v>163</v>
       </c>
-      <c r="K49" s="4" t="s">
+      <c r="K49" t="s">
+        <v>163</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
         <v>7</v>
       </c>
@@ -4400,20 +4551,23 @@
       <c r="G50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="4">
+        <v>110078</v>
+      </c>
+      <c r="I50" t="s">
         <v>564</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>555</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>565</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="L50" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="4" t="s">
         <v>7</v>
       </c>
@@ -4435,20 +4589,23 @@
       <c r="G51" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="4">
+        <v>248001</v>
+      </c>
+      <c r="I51" t="s">
         <v>566</v>
-      </c>
-      <c r="I51" t="s">
-        <v>477</v>
       </c>
       <c r="J51" t="s">
         <v>477</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="K51" t="s">
+        <v>477</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
         <v>7</v>
       </c>
@@ -4470,20 +4627,23 @@
       <c r="G52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="4">
+        <v>584101</v>
+      </c>
+      <c r="I52" t="s">
         <v>567</v>
-      </c>
-      <c r="I52" t="s">
-        <v>171</v>
       </c>
       <c r="J52" t="s">
         <v>171</v>
       </c>
-      <c r="K52" s="4" t="s">
+      <c r="K52" t="s">
+        <v>171</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" s="5" t="s">
         <v>7</v>
       </c>
@@ -4505,20 +4665,23 @@
       <c r="G53" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="4">
+        <v>600045</v>
+      </c>
+      <c r="I53" t="s">
         <v>568</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>176</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>569</v>
       </c>
-      <c r="K53" s="4" t="s">
+      <c r="L53" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A54" s="5" t="s">
         <v>7</v>
       </c>
@@ -4540,20 +4703,23 @@
       <c r="G54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="4">
+        <v>212601</v>
+      </c>
+      <c r="I54" t="s">
         <v>570</v>
-      </c>
-      <c r="I54" t="s">
-        <v>180</v>
       </c>
       <c r="J54" t="s">
         <v>180</v>
       </c>
-      <c r="K54" s="4" t="s">
+      <c r="K54" t="s">
+        <v>180</v>
+      </c>
+      <c r="L54" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55" s="5" t="s">
         <v>7</v>
       </c>
@@ -4575,20 +4741,23 @@
       <c r="G55" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="4">
+        <v>411039</v>
+      </c>
+      <c r="I55" t="s">
         <v>571</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>332</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>572</v>
       </c>
-      <c r="K55" s="4" t="s">
+      <c r="L55" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A56" s="5" t="s">
         <v>7</v>
       </c>
@@ -4610,20 +4779,23 @@
       <c r="G56" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="4">
+        <v>585202</v>
+      </c>
+      <c r="I56" t="s">
         <v>516</v>
       </c>
-      <c r="I56" t="s">
+      <c r="J56" t="s">
         <v>46</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>517</v>
       </c>
-      <c r="K56" s="4" t="s">
+      <c r="L56" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A57" s="4" t="s">
         <v>7</v>
       </c>
@@ -4645,20 +4817,23 @@
       <c r="G57" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="4">
+        <v>411013</v>
+      </c>
+      <c r="I57" t="s">
         <v>573</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>332</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>574</v>
       </c>
-      <c r="K57" s="4" t="s">
+      <c r="L57" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
         <v>7</v>
       </c>
@@ -4680,20 +4855,23 @@
       <c r="G58" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="4">
+        <v>124105</v>
+      </c>
+      <c r="I58" t="s">
         <v>575</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>555</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>576</v>
       </c>
-      <c r="K58" s="4" t="s">
+      <c r="L58" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A59" s="4" t="s">
         <v>7</v>
       </c>
@@ -4715,20 +4893,23 @@
       <c r="G59" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="4">
+        <v>743337</v>
+      </c>
+      <c r="I59" t="s">
         <v>559</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>156</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>560</v>
       </c>
-      <c r="K59" s="4" t="s">
+      <c r="L59" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
         <v>7</v>
       </c>
@@ -4750,20 +4931,23 @@
       <c r="G60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="4">
+        <v>400708</v>
+      </c>
+      <c r="I60" t="s">
         <v>544</v>
       </c>
-      <c r="I60" t="s">
+      <c r="J60" t="s">
         <v>436</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>545</v>
       </c>
-      <c r="K60" s="4" t="s">
+      <c r="L60" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61" s="4" t="s">
         <v>7</v>
       </c>
@@ -4785,20 +4969,23 @@
       <c r="G61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="4">
+        <v>560032</v>
+      </c>
+      <c r="I61" t="s">
         <v>521</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>501</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>522</v>
       </c>
-      <c r="K61" s="4" t="s">
+      <c r="L61" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
         <v>7</v>
       </c>
@@ -4820,20 +5007,23 @@
       <c r="G62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="4">
+        <v>560099</v>
+      </c>
+      <c r="I62" t="s">
         <v>577</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>501</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>578</v>
       </c>
-      <c r="K62" s="4" t="s">
+      <c r="L62" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A63" s="4" t="s">
         <v>7</v>
       </c>
@@ -4855,20 +5045,23 @@
       <c r="G63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="4">
+        <v>500062</v>
+      </c>
+      <c r="I63" t="s">
         <v>546</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>530</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>547</v>
       </c>
-      <c r="K63" s="4" t="s">
+      <c r="L63" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A64" s="4" t="s">
         <v>7</v>
       </c>
@@ -4890,20 +5083,23 @@
       <c r="G64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="4">
+        <v>400708</v>
+      </c>
+      <c r="I64" t="s">
         <v>544</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>436</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>545</v>
       </c>
-      <c r="K64" s="4" t="s">
+      <c r="L64" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A65" s="4" t="s">
         <v>7</v>
       </c>
@@ -4925,20 +5121,23 @@
       <c r="G65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="4">
+        <v>411033</v>
+      </c>
+      <c r="I65" t="s">
         <v>571</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>332</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>572</v>
       </c>
-      <c r="K65" s="4" t="s">
+      <c r="L65" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A66" s="4" t="s">
         <v>7</v>
       </c>
@@ -4960,20 +5159,23 @@
       <c r="G66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="4">
+        <v>786190</v>
+      </c>
+      <c r="I66" t="s">
         <v>529</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>530</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>531</v>
       </c>
-      <c r="K66" s="4" t="s">
+      <c r="L66" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A67" s="4" t="s">
         <v>7</v>
       </c>
@@ -4995,20 +5197,23 @@
       <c r="G67" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="4">
+        <v>600032</v>
+      </c>
+      <c r="I67" t="s">
         <v>579</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>176</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>580</v>
       </c>
-      <c r="K67" s="4" t="s">
+      <c r="L67" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A68" s="4" t="s">
         <v>7</v>
       </c>
@@ -5030,20 +5235,23 @@
       <c r="G68" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="4">
+        <v>560085</v>
+      </c>
+      <c r="I68" t="s">
         <v>509</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>501</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>510</v>
       </c>
-      <c r="K68" s="4" t="s">
+      <c r="L68" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A69" s="4" t="s">
         <v>7</v>
       </c>
@@ -5065,20 +5273,23 @@
       <c r="G69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="4">
+        <v>201003</v>
+      </c>
+      <c r="I69" t="s">
         <v>581</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>555</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>582</v>
       </c>
-      <c r="K69" s="4" t="s">
+      <c r="L69" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A70" s="4" t="s">
         <v>7</v>
       </c>
@@ -5100,20 +5311,23 @@
       <c r="G70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="4">
+        <v>560057</v>
+      </c>
+      <c r="I70" t="s">
         <v>523</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>501</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>524</v>
       </c>
-      <c r="K70" s="4" t="s">
+      <c r="L70" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A71" s="4" t="s">
         <v>7</v>
       </c>
@@ -5135,20 +5349,23 @@
       <c r="G71" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="4">
+        <v>632109</v>
+      </c>
+      <c r="I71" t="s">
         <v>552</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>50</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>553</v>
       </c>
-      <c r="K71" s="4" t="s">
+      <c r="L71" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A72" s="4" t="s">
         <v>7</v>
       </c>
@@ -5170,20 +5387,23 @@
       <c r="G72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="4">
+        <v>600073</v>
+      </c>
+      <c r="I72" t="s">
         <v>568</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>176</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>569</v>
       </c>
-      <c r="K72" s="4" t="s">
+      <c r="L72" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A73" s="4" t="s">
         <v>7</v>
       </c>
@@ -5205,20 +5425,23 @@
       <c r="G73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="4">
+        <v>560024</v>
+      </c>
+      <c r="I73" t="s">
         <v>521</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>501</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>522</v>
       </c>
-      <c r="K73" s="4" t="s">
+      <c r="L73" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A74" s="4" t="s">
         <v>7</v>
       </c>
@@ -5240,20 +5463,23 @@
       <c r="G74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="4">
+        <v>500070</v>
+      </c>
+      <c r="I74" t="s">
         <v>583</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>530</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>584</v>
       </c>
-      <c r="K74" s="4" t="s">
+      <c r="L74" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A75" s="4" t="s">
         <v>7</v>
       </c>
@@ -5275,20 +5501,23 @@
       <c r="G75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="4">
+        <v>201301</v>
+      </c>
+      <c r="I75" t="s">
         <v>581</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>555</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>582</v>
       </c>
-      <c r="K75" s="4" t="s">
+      <c r="L75" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A76" s="4" t="s">
         <v>7</v>
       </c>
@@ -5310,20 +5539,23 @@
       <c r="G76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="4">
+        <v>603201</v>
+      </c>
+      <c r="I76" t="s">
         <v>585</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>176</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>586</v>
       </c>
-      <c r="K76" s="4" t="s">
+      <c r="L76" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A77" s="4" t="s">
         <v>7</v>
       </c>
@@ -5345,20 +5577,23 @@
       <c r="G77" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="4">
+        <v>641044</v>
+      </c>
+      <c r="I77" t="s">
         <v>587</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>485</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>588</v>
       </c>
-      <c r="K77" s="4" t="s">
+      <c r="L77" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A78" s="4" t="s">
         <v>7</v>
       </c>
@@ -5380,20 +5615,23 @@
       <c r="G78" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="4">
+        <v>562106</v>
+      </c>
+      <c r="I78" t="s">
         <v>577</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>501</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>578</v>
       </c>
-      <c r="K78" s="4" t="s">
+      <c r="L78" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A79" s="4" t="s">
         <v>7</v>
       </c>
@@ -5415,20 +5653,23 @@
       <c r="G79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="4">
+        <v>411006</v>
+      </c>
+      <c r="I79" t="s">
         <v>573</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>332</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>574</v>
       </c>
-      <c r="K79" s="4" t="s">
+      <c r="L79" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A80" s="4" t="s">
         <v>7</v>
       </c>
@@ -5450,20 +5691,23 @@
       <c r="G80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="4">
+        <v>380024</v>
+      </c>
+      <c r="I80" t="s">
         <v>589</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>590</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>591</v>
       </c>
-      <c r="K80" s="4" t="s">
+      <c r="L80" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A81" s="4" t="s">
         <v>7</v>
       </c>
@@ -5485,20 +5729,23 @@
       <c r="G81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="4">
+        <v>382424</v>
+      </c>
+      <c r="I81" t="s">
         <v>592</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>590</v>
       </c>
-      <c r="J81" t="s">
+      <c r="K81" t="s">
         <v>593</v>
       </c>
-      <c r="K81" s="4" t="s">
+      <c r="L81" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A82" s="4" t="s">
         <v>7</v>
       </c>
@@ -5520,20 +5767,23 @@
       <c r="G82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="4">
+        <v>160002</v>
+      </c>
+      <c r="I82" t="s">
         <v>525</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>526</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>527</v>
       </c>
-      <c r="K82" s="4" t="s">
+      <c r="L82" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A83" s="4" t="s">
         <v>7</v>
       </c>
@@ -5555,20 +5805,23 @@
       <c r="G83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="4">
+        <v>400101</v>
+      </c>
+      <c r="I83" t="s">
         <v>594</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>436</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>595</v>
       </c>
-      <c r="K83" s="4" t="s">
+      <c r="L83" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A84" s="4" t="s">
         <v>7</v>
       </c>
@@ -5590,20 +5843,23 @@
       <c r="G84" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="4">
+        <v>520001</v>
+      </c>
+      <c r="I84" t="s">
         <v>596</v>
-      </c>
-      <c r="I84" t="s">
-        <v>399</v>
       </c>
       <c r="J84" t="s">
         <v>399</v>
       </c>
-      <c r="K84" s="4" t="s">
+      <c r="K84" t="s">
+        <v>399</v>
+      </c>
+      <c r="L84" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A85" s="4" t="s">
         <v>7</v>
       </c>
@@ -5625,20 +5881,23 @@
       <c r="G85" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="4">
+        <v>517501</v>
+      </c>
+      <c r="I85" t="s">
         <v>597</v>
-      </c>
-      <c r="I85" t="s">
-        <v>401</v>
       </c>
       <c r="J85" t="s">
         <v>401</v>
       </c>
-      <c r="K85" s="4" t="s">
+      <c r="K85" t="s">
+        <v>401</v>
+      </c>
+      <c r="L85" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A86" s="4" t="s">
         <v>7</v>
       </c>
@@ -5660,20 +5919,23 @@
       <c r="G86" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="4">
+        <v>530001</v>
+      </c>
+      <c r="I86" t="s">
         <v>598</v>
-      </c>
-      <c r="I86" t="s">
-        <v>599</v>
       </c>
       <c r="J86" t="s">
         <v>599</v>
       </c>
-      <c r="K86" s="4" t="s">
+      <c r="K86" t="s">
+        <v>599</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A87" s="4" t="s">
         <v>7</v>
       </c>
@@ -5695,20 +5957,23 @@
       <c r="G87" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="4">
+        <v>786125</v>
+      </c>
+      <c r="I87" t="s">
         <v>529</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>530</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>531</v>
       </c>
-      <c r="K87" s="4" t="s">
+      <c r="L87" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A88" s="4" t="s">
         <v>7</v>
       </c>
@@ -5730,20 +5995,23 @@
       <c r="G88" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="4">
+        <v>784001</v>
+      </c>
+      <c r="I88" t="s">
         <v>600</v>
-      </c>
-      <c r="I88" t="s">
-        <v>406</v>
       </c>
       <c r="J88" t="s">
         <v>406</v>
       </c>
-      <c r="K88" s="4" t="s">
+      <c r="K88" t="s">
+        <v>406</v>
+      </c>
+      <c r="L88" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A89" s="4" t="s">
         <v>7</v>
       </c>
@@ -5765,20 +6033,23 @@
       <c r="G89" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="4">
+        <v>783380</v>
+      </c>
+      <c r="I89" t="s">
         <v>601</v>
-      </c>
-      <c r="I89" t="s">
-        <v>408</v>
       </c>
       <c r="J89" t="s">
         <v>408</v>
       </c>
-      <c r="K89" s="4" t="s">
+      <c r="K89" t="s">
+        <v>408</v>
+      </c>
+      <c r="L89" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A90" s="4" t="s">
         <v>7</v>
       </c>
@@ -5800,20 +6071,23 @@
       <c r="G90" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="4">
+        <v>785001</v>
+      </c>
+      <c r="I90" t="s">
         <v>602</v>
-      </c>
-      <c r="I90" t="s">
-        <v>410</v>
       </c>
       <c r="J90" t="s">
         <v>410</v>
       </c>
-      <c r="K90" s="4" t="s">
+      <c r="K90" t="s">
+        <v>410</v>
+      </c>
+      <c r="L90" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A91" s="4" t="s">
         <v>7</v>
       </c>
@@ -5835,20 +6109,23 @@
       <c r="G91" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="4">
+        <v>786001</v>
+      </c>
+      <c r="I91" t="s">
         <v>603</v>
-      </c>
-      <c r="I91" t="s">
-        <v>412</v>
       </c>
       <c r="J91" t="s">
         <v>412</v>
       </c>
-      <c r="K91" s="4" t="s">
+      <c r="K91" t="s">
+        <v>412</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A92" s="4" t="s">
         <v>7</v>
       </c>
@@ -5870,20 +6147,23 @@
       <c r="G92" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="4">
+        <v>781301</v>
+      </c>
+      <c r="I92" t="s">
         <v>604</v>
-      </c>
-      <c r="I92" t="s">
-        <v>414</v>
       </c>
       <c r="J92" t="s">
         <v>414</v>
       </c>
-      <c r="K92" s="4" t="s">
+      <c r="K92" t="s">
+        <v>414</v>
+      </c>
+      <c r="L92" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A93" s="4" t="s">
         <v>7</v>
       </c>
@@ -5905,20 +6185,23 @@
       <c r="G93" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="4">
+        <v>788001</v>
+      </c>
+      <c r="I93" t="s">
         <v>605</v>
-      </c>
-      <c r="I93" t="s">
-        <v>416</v>
       </c>
       <c r="J93" t="s">
         <v>416</v>
       </c>
-      <c r="K93" s="4" t="s">
+      <c r="K93" t="s">
+        <v>416</v>
+      </c>
+      <c r="L93" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A94" s="4" t="s">
         <v>7</v>
       </c>
@@ -5940,20 +6223,23 @@
       <c r="G94" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="4">
+        <v>854301</v>
+      </c>
+      <c r="I94" t="s">
         <v>606</v>
-      </c>
-      <c r="I94" t="s">
-        <v>418</v>
       </c>
       <c r="J94" t="s">
         <v>418</v>
       </c>
-      <c r="K94" s="4" t="s">
+      <c r="K94" t="s">
+        <v>418</v>
+      </c>
+      <c r="L94" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A95" s="4" t="s">
         <v>7</v>
       </c>
@@ -5975,20 +6261,23 @@
       <c r="G95" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="4">
+        <v>842001</v>
+      </c>
+      <c r="I95" t="s">
         <v>607</v>
-      </c>
-      <c r="I95" t="s">
-        <v>420</v>
       </c>
       <c r="J95" t="s">
         <v>420</v>
       </c>
-      <c r="K95" s="4" t="s">
+      <c r="K95" t="s">
+        <v>420</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A96" s="4" t="s">
         <v>7</v>
       </c>
@@ -6010,20 +6299,23 @@
       <c r="G96" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="4">
+        <v>812001</v>
+      </c>
+      <c r="I96" t="s">
         <v>608</v>
-      </c>
-      <c r="I96" t="s">
-        <v>422</v>
       </c>
       <c r="J96" t="s">
         <v>422</v>
       </c>
-      <c r="K96" s="4" t="s">
+      <c r="K96" t="s">
+        <v>422</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A97" s="4" t="s">
         <v>7</v>
       </c>
@@ -6045,20 +6337,23 @@
       <c r="G97" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="4">
+        <v>800001</v>
+      </c>
+      <c r="I97" t="s">
         <v>609</v>
-      </c>
-      <c r="I97" t="s">
-        <v>494</v>
       </c>
       <c r="J97" t="s">
         <v>494</v>
       </c>
-      <c r="K97" s="4" t="s">
+      <c r="K97" t="s">
+        <v>494</v>
+      </c>
+      <c r="L97" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A98" s="4" t="s">
         <v>7</v>
       </c>
@@ -6080,20 +6375,23 @@
       <c r="G98" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="4">
+        <v>824101</v>
+      </c>
+      <c r="I98" t="s">
         <v>610</v>
-      </c>
-      <c r="I98" t="s">
-        <v>611</v>
       </c>
       <c r="J98" t="s">
         <v>611</v>
       </c>
-      <c r="K98" s="4" t="s">
+      <c r="K98" t="s">
+        <v>611</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A99" s="4" t="s">
         <v>7</v>
       </c>
@@ -6115,20 +6413,23 @@
       <c r="G99" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="4">
+        <v>560062</v>
+      </c>
+      <c r="I99" t="s">
         <v>509</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>501</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>510</v>
       </c>
-      <c r="K99" s="4" t="s">
+      <c r="L99" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A100" s="4" t="s">
         <v>7</v>
       </c>
@@ -6150,20 +6451,23 @@
       <c r="G100" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="4">
+        <v>560078</v>
+      </c>
+      <c r="I100" t="s">
         <v>509</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>501</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>510</v>
       </c>
-      <c r="K100" s="4" t="s">
+      <c r="L100" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A101" s="4" t="s">
         <v>7</v>
       </c>
@@ -6185,20 +6489,23 @@
       <c r="G101" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="4">
+        <v>570001</v>
+      </c>
+      <c r="I101" t="s">
         <v>541</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>542</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>543</v>
       </c>
-      <c r="K101" s="4" t="s">
+      <c r="L101" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A102" s="4" t="s">
         <v>7</v>
       </c>
@@ -6220,20 +6527,23 @@
       <c r="G102" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="4">
+        <v>585101</v>
+      </c>
+      <c r="I102" t="s">
         <v>516</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>46</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>517</v>
       </c>
-      <c r="K102" s="4" t="s">
+      <c r="L102" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A103" s="4" t="s">
         <v>7</v>
       </c>
@@ -6255,20 +6565,23 @@
       <c r="G103" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="4">
+        <v>580001</v>
+      </c>
+      <c r="I103" t="s">
         <v>612</v>
-      </c>
-      <c r="I103" t="s">
-        <v>613</v>
       </c>
       <c r="J103" t="s">
         <v>613</v>
       </c>
-      <c r="K103" s="4" t="s">
+      <c r="K103" t="s">
+        <v>613</v>
+      </c>
+      <c r="L103" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A104" s="4" t="s">
         <v>7</v>
       </c>
@@ -6290,20 +6603,23 @@
       <c r="G104" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="4">
+        <v>400001</v>
+      </c>
+      <c r="I104" t="s">
         <v>614</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>436</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>615</v>
       </c>
-      <c r="K104" s="4" t="s">
+      <c r="L104" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A105" s="4" t="s">
         <v>7</v>
       </c>
@@ -6325,20 +6641,23 @@
       <c r="G105" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="4">
+        <v>412207</v>
+      </c>
+      <c r="I105" t="s">
         <v>557</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>332</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>558</v>
       </c>
-      <c r="K105" s="4" t="s">
+      <c r="L105" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A106" s="4" t="s">
         <v>7</v>
       </c>
@@ -6360,20 +6679,23 @@
       <c r="G106" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="4">
+        <v>411013</v>
+      </c>
+      <c r="I106" t="s">
         <v>573</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>332</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>574</v>
       </c>
-      <c r="K106" s="4" t="s">
+      <c r="L106" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A107" s="4" t="s">
         <v>7</v>
       </c>
@@ -6395,20 +6717,23 @@
       <c r="G107" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="4">
+        <v>411043</v>
+      </c>
+      <c r="I107" t="s">
         <v>616</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>332</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>617</v>
       </c>
-      <c r="K107" s="4" t="s">
+      <c r="L107" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A108" s="4" t="s">
         <v>7</v>
       </c>
@@ -6430,20 +6755,23 @@
       <c r="G108" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="4">
+        <v>500007</v>
+      </c>
+      <c r="I108" t="s">
         <v>546</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>530</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>547</v>
       </c>
-      <c r="K108" s="4" t="s">
+      <c r="L108" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A109" s="4" t="s">
         <v>7</v>
       </c>
@@ -6465,20 +6793,23 @@
       <c r="G109" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="4">
+        <v>500072</v>
+      </c>
+      <c r="I109" t="s">
         <v>583</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>530</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>584</v>
       </c>
-      <c r="K109" s="4" t="s">
+      <c r="L109" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A110" s="4" t="s">
         <v>7</v>
       </c>
@@ -6500,20 +6831,23 @@
       <c r="G110" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="4">
+        <v>626001</v>
+      </c>
+      <c r="I110" t="s">
         <v>579</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>176</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>580</v>
       </c>
-      <c r="K110" s="4" t="s">
+      <c r="L110" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A111" s="4" t="s">
         <v>7</v>
       </c>
@@ -6535,20 +6869,23 @@
       <c r="G111" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="4">
+        <v>413501</v>
+      </c>
+      <c r="I111" t="s">
         <v>618</v>
-      </c>
-      <c r="I111" t="s">
-        <v>278</v>
       </c>
       <c r="J111" t="s">
         <v>278</v>
       </c>
-      <c r="K111" s="4" t="s">
+      <c r="K111" t="s">
+        <v>278</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A112" s="4" t="s">
         <v>7</v>
       </c>
@@ -6570,20 +6907,23 @@
       <c r="G112" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="4">
+        <v>500039</v>
+      </c>
+      <c r="I112" t="s">
         <v>546</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>530</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>547</v>
       </c>
-      <c r="K112" s="4" t="s">
+      <c r="L112" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A113" s="4" t="s">
         <v>7</v>
       </c>
@@ -6605,20 +6945,23 @@
       <c r="G113" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="4">
+        <v>560058</v>
+      </c>
+      <c r="I113" t="s">
         <v>523</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>501</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>524</v>
       </c>
-      <c r="K113" s="4" t="s">
+      <c r="L113" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A114" s="4" t="s">
         <v>7</v>
       </c>
@@ -6640,20 +6983,23 @@
       <c r="G114" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="4">
+        <v>560004</v>
+      </c>
+      <c r="I114" t="s">
         <v>509</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>501</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>510</v>
       </c>
-      <c r="K114" s="4" t="s">
+      <c r="L114" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A115" s="4" t="s">
         <v>7</v>
       </c>
@@ -6675,20 +7021,23 @@
       <c r="G115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="4">
+        <v>562114</v>
+      </c>
+      <c r="I115" t="s">
         <v>500</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>501</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>502</v>
       </c>
-      <c r="K115" s="4" t="s">
+      <c r="L115" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A116" s="4" t="s">
         <v>7</v>
       </c>
@@ -6710,20 +7059,23 @@
       <c r="G116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="4">
+        <v>400710</v>
+      </c>
+      <c r="I116" t="s">
         <v>544</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>436</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>545</v>
       </c>
-      <c r="K116" s="4" t="s">
+      <c r="L116" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A117" s="11" t="s">
         <v>7</v>
       </c>
@@ -6745,20 +7097,23 @@
       <c r="G117" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="4">
+        <v>733134</v>
+      </c>
+      <c r="I117" t="s">
         <v>619</v>
-      </c>
-      <c r="I117" t="s">
-        <v>300</v>
       </c>
       <c r="J117" t="s">
         <v>300</v>
       </c>
-      <c r="K117" s="11" t="s">
+      <c r="K117" t="s">
+        <v>300</v>
+      </c>
+      <c r="L117" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A118" s="4" t="s">
         <v>7</v>
       </c>
@@ -6780,20 +7135,23 @@
       <c r="G118" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="4">
+        <v>273012</v>
+      </c>
+      <c r="I118" t="s">
         <v>620</v>
-      </c>
-      <c r="I118" t="s">
-        <v>304</v>
       </c>
       <c r="J118" t="s">
         <v>304</v>
       </c>
-      <c r="K118" s="4" t="s">
+      <c r="K118" t="s">
+        <v>304</v>
+      </c>
+      <c r="L118" s="4" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A119" s="4" t="s">
         <v>7</v>
       </c>
@@ -6815,20 +7173,23 @@
       <c r="G119" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="4">
+        <v>590008</v>
+      </c>
+      <c r="I119" t="s">
         <v>520</v>
-      </c>
-      <c r="I119" t="s">
-        <v>493</v>
       </c>
       <c r="J119" t="s">
         <v>493</v>
       </c>
-      <c r="K119" s="4" t="s">
+      <c r="K119" t="s">
+        <v>493</v>
+      </c>
+      <c r="L119" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A120" s="4" t="s">
         <v>7</v>
       </c>
@@ -6850,20 +7211,23 @@
       <c r="G120" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="4">
+        <v>515231</v>
+      </c>
+      <c r="I120" t="s">
         <v>621</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>310</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>622</v>
       </c>
-      <c r="K120" s="14" t="s">
+      <c r="L120" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A121" s="4" t="s">
         <v>7</v>
       </c>
@@ -6885,20 +7249,23 @@
       <c r="G121" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="4">
+        <v>382110</v>
+      </c>
+      <c r="I121" t="s">
         <v>592</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>590</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>593</v>
       </c>
-      <c r="K121" s="14" t="s">
+      <c r="L121" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A122" s="4" t="s">
         <v>7</v>
       </c>
@@ -6920,20 +7287,23 @@
       <c r="G122" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H122" s="4">
+        <v>601204</v>
+      </c>
+      <c r="I122" t="s">
         <v>579</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>176</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>580</v>
       </c>
-      <c r="K122" s="14" t="s">
+      <c r="L122" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A123" s="4" t="s">
         <v>7</v>
       </c>
@@ -6955,20 +7325,23 @@
       <c r="G123" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H123" t="s">
+      <c r="H123" s="4">
+        <v>562109</v>
+      </c>
+      <c r="I123" t="s">
         <v>623</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>501</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>624</v>
       </c>
-      <c r="K123" s="14" t="s">
+      <c r="L123" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A124" s="4" t="s">
         <v>7</v>
       </c>
@@ -6990,20 +7363,23 @@
       <c r="G124" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" s="4">
+        <v>363750</v>
+      </c>
+      <c r="I124" t="s">
         <v>625</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>626</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>328</v>
       </c>
-      <c r="K124" s="14" t="s">
+      <c r="L124" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A125" s="4" t="s">
         <v>7</v>
       </c>
@@ -7025,20 +7401,23 @@
       <c r="G125" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H125" t="s">
+      <c r="H125" s="4">
+        <v>410501</v>
+      </c>
+      <c r="I125" t="s">
         <v>557</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>332</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>558</v>
       </c>
-      <c r="K125" s="14" t="s">
+      <c r="L125" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A126" s="4" t="s">
         <v>7</v>
       </c>
@@ -7060,76 +7439,79 @@
       <c r="G126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H126" t="s">
+      <c r="H126" s="4">
+        <v>422009</v>
+      </c>
+      <c r="I126" t="s">
         <v>627</v>
-      </c>
-      <c r="I126" t="s">
-        <v>338</v>
       </c>
       <c r="J126" t="s">
         <v>338</v>
       </c>
-      <c r="K126" s="4" t="s">
+      <c r="K126" t="s">
+        <v>338</v>
+      </c>
+      <c r="L126" s="4" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B126 C2:C6">
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C26">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C27">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38:C44">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C51">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C53">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C112">
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C115:C118">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C119 C126">
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K45 K47 K49 K59">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B126 C2:C6">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="L45 L47 L49 L59">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G73 K2:K73" xr:uid="{0A916525-D2E7-410A-851E-5D90B6CAD0BD}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L73 G2:G73" xr:uid="{0A916525-D2E7-410A-851E-5D90B6CAD0BD}">
       <formula1>"Replaced,Active,In- Active,Closing Shortly,Opeing Shortly,Closed"</formula1>
     </dataValidation>
   </dataValidations>
